--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0081.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0081.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Baby Roseshroom</t>
+          <t>Nấm Hồng Bé Nhỏ</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Mutant Flora</t>
+          <t>Thực vật đột biến</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Mutant Flora</t>
+          <t>Thực vật đột biến</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Mutant Flora</t>
+          <t>Thực vật đột biến</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Discord - Natural Species</t>
+          <t>Tacet Discord - Loài Tự Nhiên</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Discord - Natural Species</t>
+          <t>Tacet Discord - Loài Tự Nhiên</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Discord - Natural Species</t>
+          <t>Tacet Discord - Loài Tự Nhiên</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Discord - Natural Species</t>
+          <t>Tacet Discord - Loài Tự Nhiên</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Discord - Natural Species</t>
+          <t>Tacet Discord - Loài Tự Nhiên</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Rock Guardian</t>
+          <t>Người Bảo Vệ Đá</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Mutant Flora</t>
+          <t>Thực vật đột biến</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Mutant Flora</t>
+          <t>Thực vật đột biến</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Spearback</t>
+          <t>Lưng Lao</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Mutant Flora</t>
+          <t>Thực vật đột biến</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Calamity Class</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Hoochief (Young)</t>
+          <t>Thủ Lĩnh Hoo (Trẻ)</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Thundering Mephis (Form I)</t>
+          <t>Mephis Sấm Sét (Hình Thái I)</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Discord - Disordered Species</t>
+          <t>Tacet Discord - Loài Rối Loạn</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hoochief (Mature)</t>
+          <t>Thủ Lĩnh Hoo (Trưởng thành)</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Calamity Class</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Crownless (Clone)</t>
+          <t>Crownless (Bản Sao)</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Discord - Threnodian Species</t>
+          <t>Tacet Discord - Loài Threnodian</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Discord - Disordered Species</t>
+          <t>Tacet Discord - Loài Rối Loạn</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Discord - Disorder Species</t>
+          <t>Tacet Discord - Loài Hỗn Loạn</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Discord - Artificial Species</t>
+          <t>Tacet Discord - Loài Nhân Tạo</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Mainstats</t>
+          <t>Chỉ Số Chính</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Mutant Fauna</t>
+          <t>Sinh vật đột biến</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Đường Giới Hạn Của Thần Linh</t>
+          <t>Giới Hạn Được Vẽ Bởi Thần Linh</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Trách Nhiệm</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>New Solar Ceremony</t>
+          <t>Lễ Hội Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Half-Spoken Farewell</t>
+          <t>Lời Tạm Biệt Nửa Vời</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Tấn Công</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Nguồn Cơn Của Nỗi Sợ Và Kinh Hoàng</t>
+          <t>Nguồn Cội Của Nỗi Sợ Và Kinh Hoàng</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>The Savior</t>
+          <t>Vị Cứu Tinh</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>A Burning Heart</t>
+          <t>Trái Tim Cháy Bỏng</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Cùng Nhau Qua Gió Tuyết</t>
+          <t>Cùng Vượt Gió Tuyết</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Emerging Sharpness</t>
+          <t>Sắc Nhọn Hiện Hữu</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Biến Thể Của Âm Thanh Kỳ Lạ</t>
+          <t>Biến thể của Âm Thanh Kỳ Lạ</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>First Meet Jinhsi</t>
+          <t>Gặp Gỡ Jinhsi Lần Đầu</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Temporary Squad</t>
+          <t>Đội Hình Tạm Thời</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Sum Vầy Trong Ánh Sáng</t>
+          <t>Đoàn tụ trong Ánh Sáng</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Explosive Firewood</t>
+          <t>Củi nổ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Chương III Vùng Đất Băng Giá Roya: Ngôi Sao Du Hành Xa Xôi</t>
+          <t>Chương III Vùng Đất Băng Giá Roya: Ngôi Sao Viễn Du</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Chương III Vùng Đất Băng Giá Roya: Tất Cả Những Gì Ánh Mặt Trời Chạm Đến</t>
+          <t>Chương III Vùng Đất Băng Giá Roya: Ánh Dương Chạm Đến Nơi Đây</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính - Huanglong - Khúc Dạo Đầu Còn Lại</t>
+          <t>Nhiệm vụ chính - Huanglong - Khúc Dạo Dư Âm</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính - Huanglong - The Discord</t>
+          <t>Nhiệm vụ chính - Huanglong - Tacet Discord</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính - Huanglong - Darkness Incept</t>
+          <t>Nhiệm vụ chính - Huanglong - Bóng Tối Khởi Đầu</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính - Huanglong - Uneasy Bindings</t>
+          <t>Nhiệm vụ chính - Huanglong - Những Ràng Buộc Bất An</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính - Huanglong - Voices Within the Fog</t>
+          <t>Nhiệm Vụ Chính - Huanglong - Tiếng Gọi Trong Sương Mù</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Chương III Lahai-Roi: Wishes in the Bell</t>
+          <t>Chương III Lahai-Roi: Lời Nguyện Trong Chuông</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chương III Lahai-Roi: Starlights from Yesterdays</t>
+          <t>Chương III Lahai-Roi: Ánh Sao Từ Ngày Xưa</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Chương III Lahai-Roi: Beneath a Melting Night Sky</t>
+          <t>Lahai-Roi Chương III: Dưới bầu trời đêm tan chảy</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Chính - Huanglong - Inferno Let Loose</t>
+          <t>Nhiệm vụ chính - Huanglong - Hỏa Ngục Thả Rông</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Chương này đã bị khóa</t>
+          <t>Chương này đã bị khóa.</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Journey Log</t>
+          <t>Nhật Ký Hành Trình</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Bước Chân Phước Lành</t>
+          <t>Bước Chúc Phúc</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Lion's Majesty</t>
+          <t>Oai Phong Sư Tử</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Free Flow</t>
+          <t>Dòng Chảy Tự Do</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Kẻ Chinh Phục Ác Ma</t>
+          <t>Kẻ khuất phục Ác Ma</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tất cả Wishes Come True</t>
+          <t>Mọi Điều Ước Đều Thành Hiện Thực</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Lucky Charm</t>
+          <t>Bùa May Mắn</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Treasure Mirror</t>
+          <t>Gương Kho Báu</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Grimoire of Frost</t>
+          <t>Băng Khắc Thư</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Giấc Mơ Định Mệnh</t>
+          <t>Giấc Mộng Định Mệnh</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Gánh Nặng Của Di Vật</t>
+          <t>Sức Nặng Của Di Vật</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Khúc Aria Gương Phản Chiếu</t>
+          <t>Aria của Những Tấm Gương</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Wailed Farewell</t>
+          <t>Lời Thương Tiếc Vút Bay</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Aesthetic Deconstruction</t>
+          <t>Giải Cấu Thẩm Mỹ</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Dancer's Finale</t>
+          <t>Điệu cuối của vũ công</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Chroma Cascade</t>
+          <t>Thác Sắc Màu</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Chixia's Token</t>
+          <t>Biểu tượng của Chixia</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Woolie Combos</t>
+          <t>Kỹ Năng Combo Lông Xù</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Bữa Tiệc Hỗn Loạn</t>
+          <t>Đội Hỗn Loạn</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Cloudy's Heroic Landing</t>
+          <t>Hạ Cánh Anh Hùng của Cloudy</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Cosmos's Riot</t>
+          <t>Cosmos - Cuồng Nộ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Staccato in Prestissimo</t>
+          <t>Đoạn Nhanh Trong Prestissimo</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Requiem: Dies Irae</t>
+          <t>Khúc Ca Ngày Phán Xét: Dies Irae</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Prelude: Scorching Earth</t>
+          <t>Khúc Dạo Đầu: Đất Cháy</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Symphony: Rain of Fire</t>
+          <t>Giao Hưởng: Mưa Lửa</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Khán Giả, Hãy Cổ Vũ Cho Tôi</t>
+          <t>Hãy cổ vũ cho ta nào, khán giả ơi!</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Diễn Viên, Hãy Thắp Sáng Sân Khấu</t>
+          <t>Diễn viên, Khởi Động Sân Khấu</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Oh Sea, Burn Your Waves</t>
+          <t>Ôi Biển cả, hãy thiêu đốt những con sóng của Người</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Thuyền Trưởng, Hãy Định Hướng</t>
+          <t>Đội Trưởng, Hãy Định Hướng</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Hỡi Nhạn Biển, Hãy Ôm Trọn Bão Tố</t>
+          <t>Ôi Tern, hãy ôm lấy cơn bão đi</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Ceaseless Hunt</t>
+          <t>Săn Lùng Vô Tận</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Pack Assault</t>
+          <t>Tập Kích Đoàn</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hunter's Instinct</t>
+          <t>Bản Năng Thợ Săn</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Hunter's Bloodlust</t>
+          <t>Cơn Khát Săn Mồi</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Slaughter Spree</t>
+          <t>Đẫm Máu</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Yangyang's Token</t>
+          <t>Vật phẩm của Yangyang</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Misty Magic</t>
+          <t>Phép Thuật Sương Mù</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Veil Lifting</t>
+          <t>Gỡ Bức Màn</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Giữa Sự Thật Và Dối Trá</t>
+          <t>Giữa Chân Thật và Dối Trá</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Trong Sương Mù Dày Đặc</t>
+          <t>Sương Mù Dày Đặc</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Mist Trick</t>
+          <t>Ảo thuật Sương mù</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Jiyan's Token</t>
+          <t>Vật kỷ niệm của Jiyan</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Luminous Breeze</t>
+          <t>Gió Sáng Dịu Dàng</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Azure Scythe</t>
+          <t>Lưỡi Hái Lam</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Cerulean Tempest</t>
+          <t>Bão Tố Xanh Thẳm</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Ethereal Ascendance</t>
+          <t>Thăng Hoa Siêu Nhiên</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Lời Thì Thầm Của Bầu Trời</t>
+          <t>Lời thì thầm của bầu trời</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Sân Khấu Định Mệnh</t>
+          <t>Sân Khấu Định Mệnh Biến Dịch.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Khúc Ca Gió Zephyr</t>
+          <t>Khúc Ca Gió Nổi</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Hòa Nhịp Cùng Gió</t>
+          <t>Hóa thân cùng Gió</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Fugue</t>
+          <t>Khúc Tái Hiện</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Wind's Shadow</t>
+          <t>Bóng Gió</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc Hiện Hình</t>
+          <t>Khoảnh khắc trỗi dậy</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Blossoming Embrace</t>
+          <t>Ôm Ấp Nở Rộ</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Sự Hồi Sinh Của Sự Sống</t>
+          <t>Sự Tái Sinh Của Sự Sống</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Unhindered Light</t>
+          <t>Ánh Sáng Không Ngăn Trở</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Flying Luster</t>
+          <t>Ánh sáng bay lượn</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Lightbeam Barrage</t>
+          <t>Bão Tia Sáng</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Tactical Flash</t>
+          <t>Tia Chớp Chiến Thuật</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Undying Shimmer</t>
+          <t>Ánh Sáng Bất Diệt Lấp Lánh</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Untold Wish</t>
+          <t>Ước Nguyện Vô Danh</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Starry Sky</t>
+          <t>Bầu Trời Đầy Sao</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Tiếng Hót Của Định Mệnh</t>
+          <t>Hồi Âm Tử Thần</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Finale Sigh</t>
+          <t>Tiếng Thở Dài Cuối Cùng</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Regression Hypothesis</t>
+          <t>Giả Thuyết Hồi Quy</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Bài Thánh Ca Ánh Sáng Dệt Nên</t>
+          <t>Khúc Ca Ánh Sáng Dệt</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Stellar Proclamation</t>
+          <t>Tuyên Ngôn Tinh Tú</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Whispered Radiance</t>
+          <t>Ánh Sáng Thì Thầm</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Her Tiny Courtyard</t>
+          <t>Khu Vườn Nhỏ Của Nàng</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Final Negotiation</t>
+          <t>Thương Lượng Cuối Cùng</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Impending Deadline</t>
+          <t>Hạn Chót Sắp Tới</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Demand Breakdown</t>
+          <t>Phân Tích Nhu Cầu</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>24/7 Job</t>
+          <t>Công Việc 24/7</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Efficiency Optimization</t>
+          <t>Tối Ưu Hóa Hiệu Suất</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Nụ Hoa Chờ Đón</t>
+          <t>Nụ Hoa Chờ Hái</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Chu Trình Nở Hoa</t>
+          <t>Chu Kỳ Hoa Nở</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Greenhouse's Caress</t>
+          <t>Vuốt Ve Của Nhà Kính</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Một Ngụm Nước Mắt</t>
+          <t>Giọt Nước Mắt Nuốt Ngược</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Resurgence</t>
+          <t>Sự Trỗi Dậy</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Transitional Touch</t>
+          <t>Xúc Giác Chuyển Tiếp</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Feathered Harmony</t>
+          <t>Hòa Âm Lông Vũ</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Dưới Ánh Sáng Và Bóng Tối</t>
+          <t>Dưới Ánh Sáng và Bóng Tối</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Nghệ Thuật Nổ</t>
+          <t>Nghệ Thuật Bùng Nổ</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Tia Lóe Cảm Hứng</t>
+          <t>Tia Lóe Sáng Cảm Hứng</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Sự Hiện Thân Của Ảo Giác</t>
+          <t>Sự Biểu Hiện Của Ảo Tưởng</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Firework Brilliance</t>
+          <t>Sự rực rỡ của pháo hoa</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Spatial Magic</t>
+          <t>Phép Thuật Không Gian</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Collapsing Senses</t>
+          <t>Giác Quan Tan Vỡ</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Mirage Cleansing</t>
+          <t>Thanh Tẩy Ảo Ảnh</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Abyssal Blessing</t>
+          <t>Phúc Lành Vực Sâu</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Echoes of Drowning</t>
+          <t>Tiếng Vọng Chìm Đắm</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tiếng Ồn Từ Vực Sâu</t>
+          <t>Tiếng gầm từ vực sâu</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Retaliation Shield</t>
+          <t>Khiên Phản Đòn</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Ngọc Lục Bảo</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Unidentified Plant</t>
+          <t>Thực Vật Không Xác Định</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Aftersound Conch</t>
+          <t>Ốc Dư Âm</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Cardiotonic</t>
+          <t>Thuốc Tăng Cường Tim</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>The World</t>
+          <t>Thế Giới</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Improved Terminal</t>
+          <t>Thiết Bị Đầu Cuối Cải Tiến</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>La bàn</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Prosthetic Blade</t>
+          <t>Lưỡi Kiếm Giả</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Calculation Goggles</t>
+          <t>Kính Tính Toán</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Mechanical Wing</t>
+          <t>Cánh Cơ Khí</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Withering Dream</t>
+          <t>Giấc Mơ Tàn Úa</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Dusty Grimoire</t>
+          <t>Cuốn Cổ Ngữ Bám Bụi</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Wind Seeker</t>
+          <t>Kẻ Tìm Gió</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Rapid Grapple</t>
+          <t>Túm Nhanh</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tactical Knife I</t>
+          <t>Dao Chiến Thuật I</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Tactical Knife II</t>
+          <t>Dao Chiến Thuật II</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tactical Knife III</t>
+          <t>Dao Chiến Thuật III</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Mobile Combat Boots I</t>
+          <t>Giày Chiến Đấu Cơ Động I</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Mobile Combat Boots II</t>
+          <t>Giày Chiến Đấu Cơ Động II</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Mobile Combat Boots III</t>
+          <t>Giày Chiến Đấu Cơ Động III</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>"Tất cả-Seeing Eye"</t>
+          <t>"Con Mắt Toàn Tri"</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Blood Debt</t>
+          <t>Món nợ máu</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Hidden Blade</t>
+          <t>Lưỡi Kiếm Ẩn</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>La bàn</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Pendant: Tune Rupture</t>
+          <t>Mặt Dây Chuyền: Điệu Gãy Âm</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Pendant: Tune Strain</t>
+          <t>Mặt Dây Chuyền: Điệu Méo Tần</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Key: Blaze</t>
+          <t>Chìa Khóa: Blaze</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Key: Hurricane</t>
+          <t>Chìa Khóa: Hurricane</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Key: Thunder</t>
+          <t>Chìa Khóa: Thunder</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Key: Blizzard</t>
+          <t>Chìa Khóa: Blizzard</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Character Token 1</t>
+          <t>Mảnh ghép Nhân vật 1</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Character Token 2</t>
+          <t>Mã Nhân Vật 2</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Character Token 3</t>
+          <t>Mã Nhân Vật 3</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Thermal-Conduction Parts</t>
+          <t>Linh Kiện Dẫn Nhiệt</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Old Device II</t>
+          <t>Thiết Bị Cũ II</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Attack 1</t>
+          <t>Tấn Công</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Universal Stat 1</t>
+          <t>Chỉ số Chung 1</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Universal Stat 2</t>
+          <t>Chỉ số Chung 2</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Máu Đền Máu</t>
+          <t>Máu đền Máu</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Sweet Lotus Seed</t>
+          <t>Hạt Sen Ngọt</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Calculation Goggles</t>
+          <t>Kính Tính Toán</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>"Tất cả-Seeing Eye"</t>
+          <t>"Con Mắt Toàn Tri"</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Improved Terminal</t>
+          <t>Thiết Bị Đầu Cuối Cải Tiến</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>Lược</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Mildly Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Nhẹ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Aromatherapy</t>
+          <t>Liệu pháp hương thơm</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Super Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Cấp Siêu</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Compound Gear</t>
+          <t>Bánh Răng Ghép</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Relief Spring</t>
+          <t>Suối Giải Cảm</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Universal Stat 3</t>
+          <t>Chỉ số Chung 3</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Insulation Parts</t>
+          <t>Linh kiện cách nhiệt</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Universal Attribute 4</t>
+          <t>Thuộc Tính Chung 4</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Healing Bonus 30%</t>
+          <t>Tăng Hiệu Quả Hồi Phục 30%</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Repair Kit</t>
+          <t>Bộ Dụng Cụ Sửa Chữa</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Universal Stat 6</t>
+          <t>Chỉ số Chung 6</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Movement Speed +20%</t>
+          <t>Tốc Độ Di Chuyển +20%</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Riot Shield</t>
+          <t>Khiên Bạo Loạn</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Bạc Của Người Canh Gác</t>
+          <t>Bạc của Người Quan Sát</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Energy Drink</t>
+          <t>Nước Tăng Lực</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Prosthetic Blade</t>
+          <t>Lưỡi Kiếm Giả</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Jade Buckle</t>
+          <t>Móc Jade</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Cardiotonic</t>
+          <t>Thuốc Tăng Cường Tim</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Withering Dream</t>
+          <t>Giấc Mơ Tàn Úa</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>The Lament Epoch</t>
+          <t>Kỷ Nguyên Than Khóc</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Xoáy Lốc</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Carnival</t>
+          <t>Lễ Hội</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>Dòng Chảy</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t>Bão Sấm</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Ice Burst</t>
+          <t>Vụ nổ băng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Time Rider</t>
+          <t>Kỵ sĩ Thời gian</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Dusty Grimoire</t>
+          <t>Cuốn Cổ Ngữ Bám Bụi</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Calculation Goggles</t>
+          <t>Kính Tính Toán</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Destroyer's Promise</t>
+          <t>Lời Hứa Của Kẻ Hủy Diệt</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Energy Drink</t>
+          <t>Nước Tăng Lực</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Watcher's Promise</t>
+          <t>Lời Hứa Của Giám Thị</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Withering Dream</t>
+          <t>Giấc Mơ Tàn Úa</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Blood Debt</t>
+          <t>Món nợ máu</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Hidden Blade</t>
+          <t>Lưỡi Kiếm Ẩn</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>"Tất cả-Seeing Eye"</t>
+          <t>"Con Mắt Toàn Tri"</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Prosthetic Blade</t>
+          <t>Lưỡi Kiếm Giả</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Wonderland Phantasm</t>
+          <t>Ảo Ảnh Kỳ Diệu</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Power Hammer</t>
+          <t>Búa Năng Lượng</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>La bàn</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Aftersound Conch</t>
+          <t>Ốc Dư Âm</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Wind Seeker</t>
+          <t>Kẻ Tìm Gió</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Improved Terminal</t>
+          <t>Thiết Bị Đầu Cuối Cải Tiến</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Rapid Grapple</t>
+          <t>Túm Nhanh</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Dangerous Data</t>
+          <t>Dữ liệu nguy hiểm</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Medic Kit</t>
+          <t>Bộ Dụng Cụ Y Tế</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Phổ Biến Dạng</t>
+          <t>Phổ Bóp Méo</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Spectrum of Extremity</t>
+          <t>Phổ Cực Đoan</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cao Nguyên</t>
+          <t>Giấc Mộng Cao Nguyên</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Compound Spring</t>
+          <t>Lò Xo Ghép</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Compound Nut</t>
+          <t>Đai Ốc Ghép</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Compound Gear</t>
+          <t>Bánh Răng Ghép</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Risky Game</t>
+          <t>Trò chơi mạo hiểm</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Torridity Rescuer</t>
+          <t>Vị cứu tinh nhiệt huyết</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Resounding Bell</t>
+          <t>Chuông Vang Dội</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Timeworn Comb</t>
+          <t>Lược Cũ Mòn</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>Lược</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Unordered Cube</t>
+          <t>Khối Lập Phương Lộn Xộn</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Mặt Trời Rực Cháy Trong Rừng</t>
+          <t>Mặt Trời Nóng Rực Trong Rừng</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Mobile Combat Boots</t>
+          <t>Giày Chiến Đấu Cơ Động</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Mechanical Wing</t>
+          <t>Cánh Cơ Khí</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Cardiotonic</t>
+          <t>Thuốc Tăng Cường Tim</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Crystal of Contradiction</t>
+          <t>Pha Lê Nghịch Lý</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>The Lament Epoch</t>
+          <t>Kỷ Nguyên Than Khóc</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Blue Night Waltz</t>
+          <t>Điệu Van-xơ Đêm Xanh</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>The World</t>
+          <t>Thế Giới</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Thermal-Conduction Parts</t>
+          <t>Linh Kiện Dẫn Nhiệt</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Insulation Parts</t>
+          <t>Linh kiện cách nhiệt</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Guardian's Pledge</t>
+          <t>Lời Thề Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Guardian's Promise</t>
+          <t>Lời Hứa Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Guardian's Proof</t>
+          <t>Chứng Cứ Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Khát Khao Hủy Diệt</t>
+          <t>Khát Vọng Hủy Diệt</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Cái Giá Của Sự Phá Hủy</t>
+          <t>Giá Trị của Sự Hủy Diệt</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Old Device I</t>
+          <t>Thiết Bị Cũ I</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Old Device II</t>
+          <t>Thiết Bị Cũ II</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Moderately Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Mức Trung Bình</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Riot Shield I</t>
+          <t>Khiên Bạo Loạn I</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Ngọc Lục Bảo</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Unidentified Plant</t>
+          <t>Thực Vật Không Xác Định</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Old Revolver</t>
+          <t>Khẩu Súng Lục Cũ</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Soldier's Dog Tag</t>
+          <t>Thẻ bài của người lính</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Captain's Dog Tag</t>
+          <t>Thẻ bài của Đại úy</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Crude Nameplate</t>
+          <t>Bảng Tên Thô</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Nameplate</t>
+          <t>Bảng tên</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bảng Tên Của Kẻ Vô Danh</t>
+          <t>Bảng tên của một Kẻ Vô Danh</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Emergency Call</t>
+          <t>Cuộc Gọi Khẩn Cấp</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Prisoner Unchained</t>
+          <t>Tù Nhân Được Giải Xiềng</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Cành Cây Dưới Đáy Biển</t>
+          <t>Nhánh Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Inferior Spring</t>
+          <t>Mùa Xuân Thấp Kém</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Mùa Xuân</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Elastic Spring</t>
+          <t>Lò Xo Đàn Hồi</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Petite Tacetite Bloom</t>
+          <t>Bông Tacetite Nhỏ</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Tacetite Bloom</t>
+          <t>Tacetite Bloom tiêu chuẩn</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Brilliant Tacetite Bloom</t>
+          <t>Đóa Tacetite Rực Rỡ</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Final Barrier</t>
+          <t>Rào Chắn Cuối Cùng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Azure Tranquility</t>
+          <t>Thanh Bình Lam</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Lightweight Sabre</t>
+          <t>Kiếm Nhẹ</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Irregular Aromatherapy</t>
+          <t>Liệu Pháp Mùi Hương Bất Thường</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Dũng Khí Của Feilian</t>
+          <t>Dũng khí của Phi Liên</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Protective Device</t>
+          <t>Thiết Bị Bảo Vệ</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Emergency Call</t>
+          <t>Cuộc Gọi Khẩn Cấp</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Watcher's Promise</t>
+          <t>Lời Hứa Của Giám Thị</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Iron Conch</t>
+          <t>Ốc Sắt</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Alloy Conch</t>
+          <t>Ốc Hợp Kim</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Ngọc Lục Bảo</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>"Mercy"</t>
+          <t>"Lòng thương xót"</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Medic Kit</t>
+          <t>Bộ Dụng Cụ Y Tế</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Blue Crystal</t>
+          <t>Pha Lê Xanh</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Severely Mutated Sample</t>
+          <t>Mẫu Vật Chất Đột Biến Nặng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Tăng 50% STA tối đa</t>
+          <t>Tăng 50% Thể Lực tối đa</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tăng đáng kể STA tối đa</t>
+          <t>Thể lực tối đa tăng đáng kể</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Unlabeled Sample</t>
+          <t>Mẫu Không Nhãn</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Crystal of Contradiction</t>
+          <t>Pha Lê Nghịch Lý</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Moderately Mutated Sample</t>
+          <t>Mẫu Đột Biến Mức Trung Bình</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Soldier's Dog Tag</t>
+          <t>Thẻ bài của người lính</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Dangerous Game</t>
+          <t>Trò chơi nguy hiểm</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Lightweight Sabre</t>
+          <t>Kiếm Nhẹ</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Compound Nut</t>
+          <t>Đai Ốc Ghép</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Mechanical Wing</t>
+          <t>Cánh Cơ Khí</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Cành Cây Dưới Đáy Biển</t>
+          <t>Nhánh Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Leaping Lightning</t>
+          <t>Sấm Sét Nhảy Múa</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Final Barrier</t>
+          <t>Rào Chắn Cuối Cùng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Dũng Khí Của Feilian</t>
+          <t>Dũng khí của Phi Liên</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Torridity Rescuer</t>
+          <t>Vị cứu tinh nhiệt huyết</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dusty Book</t>
+          <t>Quyển Sách Bám Bụi</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Patterned Nut</t>
+          <t>Hạt Dinh Dưỡng Mẫu</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Captain's Dog Tag</t>
+          <t>Thẻ bài của Đại úy</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Windwaiter</t>
+          <t>Kẻ Đợi Gió</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Prisoner Unchained</t>
+          <t>Tù Nhân Được Giải Xiềng</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Blue Night Waltz</t>
+          <t>Điệu Van-xơ Đêm Xanh</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Heart of Glacio</t>
+          <t>Trái Tim Băng</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Mặt Trời Rực Cháy Trong Rừng</t>
+          <t>Mặt Trời Nóng Rực Trong Khu Rừng</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Heart of Fusion</t>
+          <t>Trái Tim Hòa Quyện</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Unordered Cube</t>
+          <t>Khối Lập Phương Lộn Xộn</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Alloy Relief Spring</t>
+          <t>Lò Xo Giảm Chấn Hợp Kim</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Resounding Bell</t>
+          <t>Chuông Vang Dội</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>The World</t>
+          <t>Thế Giới</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Broken Aromatherapy</t>
+          <t>Lư Hương Vỡ</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Moderately Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Mức Trung Bình</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Timeworn Comb</t>
+          <t>Lược Cũ Mòn</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Old Device I</t>
+          <t>Thiết Bị Cũ I</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
